--- a/artfynd/A 51774-2023 artfynd.xlsx
+++ b/artfynd/A 51774-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124126412</v>
+        <v>124126394</v>
       </c>
       <c r="B2" t="n">
-        <v>57918</v>
+        <v>56942</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103037</v>
+        <v>100091</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -767,6 +767,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett par har skymtats på åkern tidigare på dagen, är förmodligen en av dessa</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124126394</v>
+        <v>124126412</v>
       </c>
       <c r="B3" t="n">
-        <v>56942</v>
+        <v>57918</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,25 +814,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100091</v>
+        <v>103037</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -889,11 +894,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ett par har skymtats på åkern tidigare på dagen, är förmodligen en av dessa</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 51774-2023 artfynd.xlsx
+++ b/artfynd/A 51774-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124126394</v>
+        <v>124126412</v>
       </c>
       <c r="B2" t="n">
-        <v>56942</v>
+        <v>57918</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100091</v>
+        <v>103037</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -767,11 +767,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett par har skymtats på åkern tidigare på dagen, är förmodligen en av dessa</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124126412</v>
+        <v>124126394</v>
       </c>
       <c r="B3" t="n">
-        <v>57918</v>
+        <v>56942</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,25 +809,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103037</v>
+        <v>100091</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -894,6 +889,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett par har skymtats på åkern tidigare på dagen, är förmodligen en av dessa</t>
         </is>
       </c>
       <c r="AD3" t="b">
